--- a/ЛР2-3_Объем_рынка/Excel/СЦ_сценарная_оценка_Similarweb_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/СЦ_сценарная_оценка_Similarweb_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051686CD-E282-417B-BD90-ACE3014C2D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2ABBCC7-2656-4FCD-A6E5-DFA4E0D96BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,20 @@
     <sheet name="08_Источники" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1131,7 +1145,7 @@
             <c:numRef>
               <c:f>'07_Дашборд'!$E$7:$G$7</c:f>
               <c:numCache>
-                <c:formatCode>#,##0\ "BYN"</c:formatCode>
+                <c:formatCode>#\ ##0\ "BYN"</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>3.5539473519902889</c:v>
@@ -1208,7 +1222,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\ &quot;BYN&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="#\ ##0\ &quot;BYN&quot;" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1539,7 +1553,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1585,7 +1599,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="102">
+    <row r="3" spans="1:15" ht="114.75">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1606,7 +1620,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="178.5">
+    <row r="4" spans="1:15" ht="191.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1648,7 +1662,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="102">
+    <row r="6" spans="1:15" ht="114.75">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1686,7 +1700,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="25.5">
+    <row r="8" spans="1:15" ht="26.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1851,7 +1865,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="25.5">
+    <row r="13" spans="1:15" ht="38.25">
       <c r="A13" s="4">
         <v>5</v>
       </c>
@@ -2742,7 +2756,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
@@ -3082,7 +3096,7 @@
         <v>110</v>
       </c>
       <c r="B13" s="11">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>111</v>
@@ -3181,7 +3195,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" ht="25.5">
       <c r="A17" s="6" t="s">
         <v>122</v>
       </c>
@@ -4024,7 +4038,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4118,7 +4132,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="38.25">
+    <row r="4" spans="1:15" ht="39.4">
       <c r="A4" s="2" t="s">
         <v>143</v>
       </c>
@@ -5391,7 +5405,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
@@ -5476,7 +5490,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="25.5">
+    <row r="4" spans="1:15" ht="26.25">
       <c r="A4" s="2" t="s">
         <v>156</v>
       </c>
@@ -6565,7 +6579,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -6598,7 +6612,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="140.25">
+    <row r="2" spans="1:15" ht="153">
       <c r="A2" s="3" t="s">
         <v>167</v>
       </c>
@@ -6656,7 +6670,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="25.5">
+    <row r="4" spans="1:15" ht="26.25">
       <c r="A4" s="2" t="s">
         <v>156</v>
       </c>
@@ -7797,7 +7811,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -7827,7 +7841,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="165.75">
+    <row r="2" spans="1:15" ht="178.5">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -7883,7 +7897,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="25.5">
+    <row r="4" spans="1:15" ht="26.25">
       <c r="A4" s="2" t="s">
         <v>156</v>
       </c>
@@ -8969,7 +8983,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -9073,7 +9087,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="25.5">
       <c r="A5" s="6" t="s">
         <v>190</v>
       </c>
@@ -9339,15 +9353,15 @@
       </c>
       <c r="B15" s="6" t="str">
         <f>TEXT(B12,"# ##0")&amp;" – "&amp;TEXT(B14,"# ##0")</f>
-        <v xml:space="preserve"> 4 –  456</v>
+        <v>4 – 456</v>
       </c>
       <c r="C15" s="6" t="str">
         <f>TEXT(C12,"# ##0")&amp;" – "&amp;TEXT(C14,"# ##0")</f>
-        <v xml:space="preserve"> 73 – 3 960</v>
+        <v>73 – 3 960</v>
       </c>
       <c r="D15" s="6" t="str">
         <f>TEXT(D12,"# ##0")&amp;" – "&amp;TEXT(D14,"# ##0")</f>
-        <v xml:space="preserve"> 720 – 16 590</v>
+        <v>720 – 16 590</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>204</v>
@@ -10154,7 +10168,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -10223,7 +10237,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="51">
+    <row r="4" spans="1:15" ht="63.75">
       <c r="A4" s="6" t="s">
         <v>208</v>
       </c>
@@ -11321,7 +11335,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
